--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/149.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/149.xlsx
@@ -426,13 +426,13 @@
         <v>-0.5970785632973402</v>
       </c>
       <c r="E2">
-        <v>-21.2048442691165</v>
+        <v>-22.9462508348701</v>
       </c>
       <c r="F2">
-        <v>3.397302730216033</v>
+        <v>2.648327716035638</v>
       </c>
       <c r="G2">
-        <v>-12.5718508047793</v>
+        <v>-14.86655213477958</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.5077878162673892</v>
       </c>
       <c r="E3">
-        <v>-23.09613879604998</v>
+        <v>-21.57251107379925</v>
       </c>
       <c r="F3">
-        <v>3.510189326399939</v>
+        <v>2.741921635408342</v>
       </c>
       <c r="G3">
-        <v>-12.15376200862474</v>
+        <v>-13.83518477747503</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.3554929699652171</v>
       </c>
       <c r="E4">
-        <v>-23.50527736569498</v>
+        <v>-23.28266664042592</v>
       </c>
       <c r="F4">
-        <v>3.166889023657739</v>
+        <v>3.05825029551539</v>
       </c>
       <c r="G4">
-        <v>-12.94881600424503</v>
+        <v>-14.13295179600478</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.1478743495037573</v>
       </c>
       <c r="E5">
-        <v>-23.55119609213276</v>
+        <v>-24.89026585620089</v>
       </c>
       <c r="F5">
-        <v>3.767172089035624</v>
+        <v>2.449551017325063</v>
       </c>
       <c r="G5">
-        <v>-12.33695766713139</v>
+        <v>-13.74374254386206</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.1081527124048207</v>
       </c>
       <c r="E6">
-        <v>-21.69372473756257</v>
+        <v>-23.84075124865721</v>
       </c>
       <c r="F6">
-        <v>3.409335595109099</v>
+        <v>2.635963504181452</v>
       </c>
       <c r="G6">
-        <v>-10.98032921059345</v>
+        <v>-13.54824489813147</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>0.4010801542935299</v>
       </c>
       <c r="E7">
-        <v>-23.20587277820385</v>
+        <v>-25.11656275931219</v>
       </c>
       <c r="F7">
-        <v>3.862268666877007</v>
+        <v>2.120929384960471</v>
       </c>
       <c r="G7">
-        <v>-11.31576692681456</v>
+        <v>-13.22422690874808</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.7179011430641788</v>
       </c>
       <c r="E8">
-        <v>-24.25595344499848</v>
+        <v>-25.06957078453459</v>
       </c>
       <c r="F8">
-        <v>3.996787249417618</v>
+        <v>2.786177992270309</v>
       </c>
       <c r="G8">
-        <v>-11.32417902302985</v>
+        <v>-13.03927335056007</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.045001289986218</v>
       </c>
       <c r="E9">
-        <v>-25.21865720581512</v>
+        <v>-25.50954826217183</v>
       </c>
       <c r="F9">
-        <v>3.520389842598012</v>
+        <v>3.322413346798541</v>
       </c>
       <c r="G9">
-        <v>-10.39970587064283</v>
+        <v>-12.45967296918109</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.369972944212267</v>
       </c>
       <c r="E10">
-        <v>-25.63648591708084</v>
+        <v>-25.74274203119682</v>
       </c>
       <c r="F10">
-        <v>3.432910931392773</v>
+        <v>2.71352354410557</v>
       </c>
       <c r="G10">
-        <v>-10.54570092892469</v>
+        <v>-11.2960691808559</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.680805144207567</v>
       </c>
       <c r="E11">
-        <v>-25.7426741040867</v>
+        <v>-27.3700174665351</v>
       </c>
       <c r="F11">
-        <v>3.908029338942457</v>
+        <v>3.263335840365686</v>
       </c>
       <c r="G11">
-        <v>-10.33380946168364</v>
+        <v>-9.981272777752189</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.971586497970033</v>
       </c>
       <c r="E12">
-        <v>-26.71838817072737</v>
+        <v>-27.61217761409528</v>
       </c>
       <c r="F12">
-        <v>4.136620637214592</v>
+        <v>3.430104422632088</v>
       </c>
       <c r="G12">
-        <v>-10.09539059303641</v>
+        <v>-11.20330769484552</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.238630372806894</v>
       </c>
       <c r="E13">
-        <v>-27.6029214132236</v>
+        <v>-26.74239361144203</v>
       </c>
       <c r="F13">
-        <v>4.144838041850363</v>
+        <v>3.569432506313353</v>
       </c>
       <c r="G13">
-        <v>-9.697390187214145</v>
+        <v>-10.66017297258161</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.481362941649197</v>
       </c>
       <c r="E14">
-        <v>-27.95328944719705</v>
+        <v>-28.38656478330294</v>
       </c>
       <c r="F14">
-        <v>4.695324629176358</v>
+        <v>3.497338034512907</v>
       </c>
       <c r="G14">
-        <v>-9.917654024124014</v>
+        <v>-9.30268046365792</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.702778494900963</v>
       </c>
       <c r="E15">
-        <v>-27.71887299019</v>
+        <v>-29.36875909624858</v>
       </c>
       <c r="F15">
-        <v>4.496773246399344</v>
+        <v>3.178564033832795</v>
       </c>
       <c r="G15">
-        <v>-8.846417766890026</v>
+        <v>-10.36670635270738</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.908085098538527</v>
       </c>
       <c r="E16">
-        <v>-28.3776255756118</v>
+        <v>-29.70532886992067</v>
       </c>
       <c r="F16">
-        <v>4.712241548276329</v>
+        <v>3.520845444669551</v>
       </c>
       <c r="G16">
-        <v>-9.099009080990877</v>
+        <v>-9.977733804570708</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.103416445376043</v>
       </c>
       <c r="E17">
-        <v>-30.47527587036381</v>
+        <v>-30.15918612039141</v>
       </c>
       <c r="F17">
-        <v>5.101130222664196</v>
+        <v>3.629106437276224</v>
       </c>
       <c r="G17">
-        <v>-7.939672585865804</v>
+        <v>-9.147733690237871</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.299261569092996</v>
       </c>
       <c r="E18">
-        <v>-30.16392063996643</v>
+        <v>-30.57865640348492</v>
       </c>
       <c r="F18">
-        <v>4.966694476863864</v>
+        <v>4.114793156150824</v>
       </c>
       <c r="G18">
-        <v>-7.575923084192843</v>
+        <v>-8.710788026691624</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.50355718899243</v>
       </c>
       <c r="E19">
-        <v>-31.08765235347306</v>
+        <v>-30.1249961416335</v>
       </c>
       <c r="F19">
-        <v>5.033384679728447</v>
+        <v>3.931912827899972</v>
       </c>
       <c r="G19">
-        <v>-7.976353430440929</v>
+        <v>-8.341966769252499</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.722382418386238</v>
       </c>
       <c r="E20">
-        <v>-31.55403309881202</v>
+        <v>-31.11609796295224</v>
       </c>
       <c r="F20">
-        <v>5.368566981923211</v>
+        <v>3.883580903416232</v>
       </c>
       <c r="G20">
-        <v>-7.211498231229871</v>
+        <v>-8.207740700362748</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.957855111458963</v>
       </c>
       <c r="E21">
-        <v>-31.27160123190163</v>
+        <v>-32.52736518812466</v>
       </c>
       <c r="F21">
-        <v>5.376572324503865</v>
+        <v>4.659124973674019</v>
       </c>
       <c r="G21">
-        <v>-7.183497637058715</v>
+        <v>-8.579180599323436</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.206873742133707</v>
       </c>
       <c r="E22">
-        <v>-32.1233890788484</v>
+        <v>-32.38893426618418</v>
       </c>
       <c r="F22">
-        <v>5.837282109449255</v>
+        <v>4.939126409698697</v>
       </c>
       <c r="G22">
-        <v>-7.495963477782826</v>
+        <v>-7.610753333811515</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.461464668503321</v>
       </c>
       <c r="E23">
-        <v>-32.85495499783953</v>
+        <v>-33.60302720458861</v>
       </c>
       <c r="F23">
-        <v>5.715247023668832</v>
+        <v>4.67236062803595</v>
       </c>
       <c r="G23">
-        <v>-6.007062174223306</v>
+        <v>-6.978449067447336</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.714560790441984</v>
       </c>
       <c r="E24">
-        <v>-32.98524372351421</v>
+        <v>-33.77808895277713</v>
       </c>
       <c r="F24">
-        <v>6.570818011976273</v>
+        <v>4.797010041339608</v>
       </c>
       <c r="G24">
-        <v>-7.864311327209835</v>
+        <v>-7.282198241766547</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.955733635767358</v>
       </c>
       <c r="E25">
-        <v>-33.1284657709548</v>
+        <v>-33.56066333024686</v>
       </c>
       <c r="F25">
-        <v>6.167348414564329</v>
+        <v>5.019610586554696</v>
       </c>
       <c r="G25">
-        <v>-5.899270811464636</v>
+        <v>-7.747876130048128</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.176652252076291</v>
       </c>
       <c r="E26">
-        <v>-32.21514501919181</v>
+        <v>-32.39214042578161</v>
       </c>
       <c r="F26">
-        <v>6.351516025759133</v>
+        <v>4.643911177954203</v>
       </c>
       <c r="G26">
-        <v>-5.874852227566972</v>
+        <v>-7.298323909088336</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.369254966335043</v>
       </c>
       <c r="E27">
-        <v>-32.73855510194637</v>
+        <v>-33.24847938910608</v>
       </c>
       <c r="F27">
-        <v>6.363118139602742</v>
+        <v>4.536291341717297</v>
       </c>
       <c r="G27">
-        <v>-6.149862556059769</v>
+        <v>-7.400023868054747</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.526648841832732</v>
       </c>
       <c r="E28">
-        <v>-32.6052096563165</v>
+        <v>-33.3782020555298</v>
       </c>
       <c r="F28">
-        <v>6.130161345117854</v>
+        <v>4.825177846504403</v>
       </c>
       <c r="G28">
-        <v>-6.399633285361162</v>
+        <v>-6.054055368153261</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.644500296933518</v>
       </c>
       <c r="E29">
-        <v>-33.13684344786899</v>
+        <v>-33.99292428817503</v>
       </c>
       <c r="F29">
-        <v>5.846919335813425</v>
+        <v>5.117912946244914</v>
       </c>
       <c r="G29">
-        <v>-5.932839743232846</v>
+        <v>-7.287786442636836</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.724483338417056</v>
       </c>
       <c r="E30">
-        <v>-32.72239297821299</v>
+        <v>-33.5024158333232</v>
       </c>
       <c r="F30">
-        <v>5.931616589280063</v>
+        <v>5.105338329070418</v>
       </c>
       <c r="G30">
-        <v>-6.840210617363989</v>
+        <v>-7.755205677872074</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.769060055134811</v>
       </c>
       <c r="E31">
-        <v>-32.35265213243472</v>
+        <v>-32.85548935777243</v>
       </c>
       <c r="F31">
-        <v>6.070005304326554</v>
+        <v>5.222353508389876</v>
       </c>
       <c r="G31">
-        <v>-7.11860763394346</v>
+        <v>-7.374916690684914</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.785151512279255</v>
       </c>
       <c r="E32">
-        <v>-33.07953108082791</v>
+        <v>-33.84957091498821</v>
       </c>
       <c r="F32">
-        <v>6.47602627333912</v>
+        <v>4.310809734675272</v>
       </c>
       <c r="G32">
-        <v>-6.505262861882688</v>
+        <v>-7.825713676767472</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.778779741908965</v>
       </c>
       <c r="E33">
-        <v>-30.89891234954437</v>
+        <v>-33.72378122824015</v>
       </c>
       <c r="F33">
-        <v>6.018649838822596</v>
+        <v>5.028593402670655</v>
       </c>
       <c r="G33">
-        <v>-5.759234735153465</v>
+        <v>-7.162866317257977</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.754620070831321</v>
       </c>
       <c r="E34">
-        <v>-32.34037770363693</v>
+        <v>-33.06339159946457</v>
       </c>
       <c r="F34">
-        <v>5.993421081202934</v>
+        <v>4.565890565754129</v>
       </c>
       <c r="G34">
-        <v>-7.219198560154216</v>
+        <v>-7.696678543283299</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.716706572583177</v>
       </c>
       <c r="E35">
-        <v>-30.64933682579663</v>
+        <v>-33.03851669174044</v>
       </c>
       <c r="F35">
-        <v>6.023470937106889</v>
+        <v>5.168809496207722</v>
       </c>
       <c r="G35">
-        <v>-7.12097467400404</v>
+        <v>-8.275212928998636</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.669711575843975</v>
       </c>
       <c r="E36">
-        <v>-32.15817002346431</v>
+        <v>-32.25892404166096</v>
       </c>
       <c r="F36">
-        <v>5.893862916530073</v>
+        <v>4.700154011134678</v>
       </c>
       <c r="G36">
-        <v>-7.140308259953383</v>
+        <v>-8.6593884966489</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.615904934964855</v>
       </c>
       <c r="E37">
-        <v>-30.72651107983535</v>
+        <v>-32.23732548488138</v>
       </c>
       <c r="F37">
-        <v>6.097203919630073</v>
+        <v>4.951200692961902</v>
       </c>
       <c r="G37">
-        <v>-8.003089396216083</v>
+        <v>-8.945972492346987</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.559357945389561</v>
       </c>
       <c r="E38">
-        <v>-31.21526475100921</v>
+        <v>-30.26917596132672</v>
       </c>
       <c r="F38">
-        <v>5.989656979724614</v>
+        <v>4.292096915046031</v>
       </c>
       <c r="G38">
-        <v>-8.652413177197655</v>
+        <v>-8.410663899737916</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.50124786518962</v>
       </c>
       <c r="E39">
-        <v>-29.89092611288804</v>
+        <v>-30.3293842874957</v>
       </c>
       <c r="F39">
-        <v>5.979950170498609</v>
+        <v>4.968611319033942</v>
       </c>
       <c r="G39">
-        <v>-6.994677361680844</v>
+        <v>-8.172062951086023</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.440917995360389</v>
       </c>
       <c r="E40">
-        <v>-29.5093953850308</v>
+        <v>-28.89240891538174</v>
       </c>
       <c r="F40">
-        <v>6.273712445818592</v>
+        <v>5.077854755380335</v>
       </c>
       <c r="G40">
-        <v>-6.725119501691227</v>
+        <v>-8.536861895694933</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.377893802564425</v>
       </c>
       <c r="E41">
-        <v>-30.00570934356045</v>
+        <v>-29.10757030090818</v>
       </c>
       <c r="F41">
-        <v>6.494169176195236</v>
+        <v>4.878637365211471</v>
       </c>
       <c r="G41">
-        <v>-8.120739563590702</v>
+        <v>-8.405582212335135</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.313106955316535</v>
       </c>
       <c r="E42">
-        <v>-28.53611763740625</v>
+        <v>-29.15435396588142</v>
       </c>
       <c r="F42">
-        <v>6.245816345161916</v>
+        <v>4.860080278653957</v>
       </c>
       <c r="G42">
-        <v>-8.276676190126993</v>
+        <v>-8.335438373449056</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.24725906965059</v>
       </c>
       <c r="E43">
-        <v>-28.515893472488</v>
+        <v>-28.88107414494054</v>
       </c>
       <c r="F43">
-        <v>6.269732968815543</v>
+        <v>5.374862574184487</v>
       </c>
       <c r="G43">
-        <v>-7.919736480628313</v>
+        <v>-9.529684571285745</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.183584348344501</v>
       </c>
       <c r="E44">
-        <v>-27.84221956521092</v>
+        <v>-28.16528090091813</v>
       </c>
       <c r="F44">
-        <v>6.078880432680148</v>
+        <v>4.808993204188506</v>
       </c>
       <c r="G44">
-        <v>-8.91898492511085</v>
+        <v>-9.151812282342252</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.122713513009142</v>
       </c>
       <c r="E45">
-        <v>-26.59247847941811</v>
+        <v>-26.63689375248534</v>
       </c>
       <c r="F45">
-        <v>5.936540405122304</v>
+        <v>5.103315455872782</v>
       </c>
       <c r="G45">
-        <v>-7.944697993994418</v>
+        <v>-9.216593037454711</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.063527407238106</v>
       </c>
       <c r="E46">
-        <v>-27.04332882314776</v>
+        <v>-26.41086402934048</v>
       </c>
       <c r="F46">
-        <v>6.46600137103044</v>
+        <v>5.176736972252512</v>
       </c>
       <c r="G46">
-        <v>-8.507748958222583</v>
+        <v>-10.08558144660354</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.00535366867028</v>
       </c>
       <c r="E47">
-        <v>-26.23721063656835</v>
+        <v>-24.714991269734</v>
       </c>
       <c r="F47">
-        <v>5.521813294706314</v>
+        <v>5.238886065014948</v>
       </c>
       <c r="G47">
-        <v>-8.219291193749266</v>
+        <v>-9.408002159444292</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.947527784327723</v>
       </c>
       <c r="E48">
-        <v>-26.41554647146442</v>
+        <v>-26.27368296622613</v>
       </c>
       <c r="F48">
-        <v>6.131456911735833</v>
+        <v>5.215777927946453</v>
       </c>
       <c r="G48">
-        <v>-8.355371168141009</v>
+        <v>-9.272269792334175</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.888690457455073</v>
       </c>
       <c r="E49">
-        <v>-25.29810475380568</v>
+        <v>-25.71242842618947</v>
       </c>
       <c r="F49">
-        <v>5.618712400016189</v>
+        <v>5.182659799182529</v>
       </c>
       <c r="G49">
-        <v>-8.563640898562099</v>
+        <v>-10.05685253241375</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.828444252569118</v>
       </c>
       <c r="E50">
-        <v>-25.20854512335599</v>
+        <v>-25.35342459228339</v>
       </c>
       <c r="F50">
-        <v>6.039294411235165</v>
+        <v>4.952494602845075</v>
       </c>
       <c r="G50">
-        <v>-8.785103152957184</v>
+        <v>-9.556817802525611</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.763607663867173</v>
       </c>
       <c r="E51">
-        <v>-24.13281517978191</v>
+        <v>-23.02721995012725</v>
       </c>
       <c r="F51">
-        <v>5.94040391068896</v>
+        <v>5.062142282484035</v>
       </c>
       <c r="G51">
-        <v>-8.961733999659458</v>
+        <v>-8.957287937000217</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.68950006662063</v>
       </c>
       <c r="E52">
-        <v>-24.6342214073332</v>
+        <v>-23.478129164019</v>
       </c>
       <c r="F52">
-        <v>6.414244975703528</v>
+        <v>5.336918376931853</v>
       </c>
       <c r="G52">
-        <v>-9.039008753637127</v>
+        <v>-10.28384339785942</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.602152264610916</v>
       </c>
       <c r="E53">
-        <v>-23.51808841866268</v>
+        <v>-22.27729559750902</v>
       </c>
       <c r="F53">
-        <v>5.772082967909712</v>
+        <v>5.270877614111066</v>
       </c>
       <c r="G53">
-        <v>-8.574092290829578</v>
+        <v>-11.10152166169509</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.497852426228681</v>
       </c>
       <c r="E54">
-        <v>-23.249060834815</v>
+        <v>-22.97792751055376</v>
       </c>
       <c r="F54">
-        <v>5.589406418039948</v>
+        <v>5.151740157505635</v>
       </c>
       <c r="G54">
-        <v>-9.009505171791142</v>
+        <v>-10.00904825482667</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.373896297052381</v>
       </c>
       <c r="E55">
-        <v>-23.14876419249312</v>
+        <v>-22.32003986366742</v>
       </c>
       <c r="F55">
-        <v>6.057800139013706</v>
+        <v>5.042392346866489</v>
       </c>
       <c r="G55">
-        <v>-9.455932237761861</v>
+        <v>-10.63723751308554</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.229142726985996</v>
       </c>
       <c r="E56">
-        <v>-22.59826930669869</v>
+        <v>-23.12109068783225</v>
       </c>
       <c r="F56">
-        <v>5.626558696055506</v>
+        <v>5.26645247544531</v>
       </c>
       <c r="G56">
-        <v>-9.732011872463843</v>
+        <v>-9.684601549795939</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>4.061399732629076</v>
       </c>
       <c r="E57">
-        <v>-20.76491660469334</v>
+        <v>-21.93884197864974</v>
       </c>
       <c r="F57">
-        <v>5.613221980870434</v>
+        <v>5.292917157229949</v>
       </c>
       <c r="G57">
-        <v>-9.502458644770778</v>
+        <v>-10.5134231099168</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.86894428144225</v>
       </c>
       <c r="E58">
-        <v>-22.09192251400503</v>
+        <v>-21.33499714057095</v>
       </c>
       <c r="F58">
-        <v>5.89933014138855</v>
+        <v>5.042021238270035</v>
       </c>
       <c r="G58">
-        <v>-10.33862299489774</v>
+        <v>-11.46995227476058</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.651675881442565</v>
       </c>
       <c r="E59">
-        <v>-21.63461456634044</v>
+        <v>-20.98130973514987</v>
       </c>
       <c r="F59">
-        <v>5.449922601286956</v>
+        <v>4.737955729194032</v>
       </c>
       <c r="G59">
-        <v>-9.052962703085154</v>
+        <v>-10.89152713704804</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>3.409641707169181</v>
       </c>
       <c r="E60">
-        <v>-20.79837297066201</v>
+        <v>-22.26319845792314</v>
       </c>
       <c r="F60">
-        <v>6.102984267366808</v>
+        <v>4.834826670012212</v>
       </c>
       <c r="G60">
-        <v>-9.908308354066651</v>
+        <v>-10.96032027335409</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>3.145177972447115</v>
       </c>
       <c r="E61">
-        <v>-21.50803918935205</v>
+        <v>-20.73962960583451</v>
       </c>
       <c r="F61">
-        <v>5.441327461115509</v>
+        <v>5.031167968558556</v>
       </c>
       <c r="G61">
-        <v>-10.35102760903339</v>
+        <v>-11.66882336639568</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>2.862053226868057</v>
       </c>
       <c r="E62">
-        <v>-21.39168004972496</v>
+        <v>-19.60060518105523</v>
       </c>
       <c r="F62">
-        <v>5.36787446677447</v>
+        <v>4.659709801060395</v>
       </c>
       <c r="G62">
-        <v>-11.09881032489842</v>
+        <v>-11.40115913845452</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.563442670441161</v>
       </c>
       <c r="E63">
-        <v>-21.6883720812855</v>
+        <v>-19.83599073149992</v>
       </c>
       <c r="F63">
-        <v>5.515632017146624</v>
+        <v>4.91367730634989</v>
       </c>
       <c r="G63">
-        <v>-10.40312235363936</v>
+        <v>-10.55653303392918</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.252969563210548</v>
       </c>
       <c r="E64">
-        <v>-19.68421439665884</v>
+        <v>-20.5348203118896</v>
       </c>
       <c r="F64">
-        <v>5.302988448113186</v>
+        <v>4.555873947119478</v>
       </c>
       <c r="G64">
-        <v>-11.01890368721704</v>
+        <v>-11.10153490387724</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.934552638024269</v>
       </c>
       <c r="E65">
-        <v>-20.14407640366376</v>
+        <v>-20.78126892433504</v>
       </c>
       <c r="F65">
-        <v>4.570517826066167</v>
+        <v>4.846794922247859</v>
       </c>
       <c r="G65">
-        <v>-10.13852038032203</v>
+        <v>-11.54604516398073</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.611285296674938</v>
       </c>
       <c r="E66">
-        <v>-20.38030425027388</v>
+        <v>-19.20313648892799</v>
       </c>
       <c r="F66">
-        <v>4.635057587153082</v>
+        <v>4.637638779980206</v>
       </c>
       <c r="G66">
-        <v>-9.194104501606443</v>
+        <v>-11.03258948247638</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.288299351019297</v>
       </c>
       <c r="E67">
-        <v>-19.74454725586304</v>
+        <v>-20.27996685168593</v>
       </c>
       <c r="F67">
-        <v>4.625354091396689</v>
+        <v>4.669486193148235</v>
       </c>
       <c r="G67">
-        <v>-9.987072853536992</v>
+        <v>-10.48896148892712</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.9713922399013001</v>
       </c>
       <c r="E68">
-        <v>-19.4116636600332</v>
+        <v>-18.37958367741905</v>
       </c>
       <c r="F68">
-        <v>4.567444583001781</v>
+        <v>4.799675727641817</v>
       </c>
       <c r="G68">
-        <v>-9.538149636229662</v>
+        <v>-10.96486896292505</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.6655125671310861</v>
       </c>
       <c r="E69">
-        <v>-20.28185522534713</v>
+        <v>-19.95506695553161</v>
       </c>
       <c r="F69">
-        <v>4.543004431149584</v>
+        <v>4.447914480247424</v>
       </c>
       <c r="G69">
-        <v>-9.475795510997488</v>
+        <v>-11.14333054131054</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.3762014941792138</v>
       </c>
       <c r="E70">
-        <v>-19.33342521460267</v>
+        <v>-19.34488678231609</v>
       </c>
       <c r="F70">
-        <v>4.671706217787738</v>
+        <v>4.36541737060262</v>
       </c>
       <c r="G70">
-        <v>-10.11636289902769</v>
+        <v>-11.09362932112946</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.1087233416418903</v>
       </c>
       <c r="E71">
-        <v>-20.67170249571946</v>
+        <v>-19.27692344440897</v>
       </c>
       <c r="F71">
-        <v>4.351403050882059</v>
+        <v>3.867979431751907</v>
       </c>
       <c r="G71">
-        <v>-8.773708255211012</v>
+        <v>-10.50196862235092</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.1323030061557255</v>
       </c>
       <c r="E72">
-        <v>-19.5316365219184</v>
+        <v>-21.02914400609289</v>
       </c>
       <c r="F72">
-        <v>4.446526136480331</v>
+        <v>3.658351120064658</v>
       </c>
       <c r="G72">
-        <v>-10.29322879446325</v>
+        <v>-10.82834537543105</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.3411088306012837</v>
       </c>
       <c r="E73">
-        <v>-20.19613121238193</v>
+        <v>-20.85130177486366</v>
       </c>
       <c r="F73">
-        <v>4.257388320868731</v>
+        <v>4.028843411171154</v>
       </c>
       <c r="G73">
-        <v>-10.2796687999344</v>
+        <v>-10.4340891966137</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.5126115499628132</v>
       </c>
       <c r="E74">
-        <v>-20.34993177510444</v>
+        <v>-20.7857294712326</v>
       </c>
       <c r="F74">
-        <v>3.819556386853859</v>
+        <v>3.992275960541972</v>
       </c>
       <c r="G74">
-        <v>-8.545062116995709</v>
+        <v>-9.44926148850023</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.6429085008875698</v>
       </c>
       <c r="E75">
-        <v>-19.63854020781748</v>
+        <v>-22.12156590485925</v>
       </c>
       <c r="F75">
-        <v>4.302068801840932</v>
+        <v>4.138888707163457</v>
       </c>
       <c r="G75">
-        <v>-8.405148530869489</v>
+        <v>-11.20737966585882</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.7289673331058156</v>
       </c>
       <c r="E76">
-        <v>-20.16833543892285</v>
+        <v>-20.15464133352366</v>
       </c>
       <c r="F76">
-        <v>3.807654404010435</v>
+        <v>4.053079784642262</v>
       </c>
       <c r="G76">
-        <v>-8.860418063975603</v>
+        <v>-10.37750535225648</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.7682079772560368</v>
       </c>
       <c r="E77">
-        <v>-20.39481800946847</v>
+        <v>-22.7759802121817</v>
       </c>
       <c r="F77">
-        <v>3.942527527799445</v>
+        <v>3.457304694670412</v>
       </c>
       <c r="G77">
-        <v>-8.875100333442271</v>
+        <v>-9.854651031966144</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.7590662744971828</v>
       </c>
       <c r="E78">
-        <v>-21.98514109690417</v>
+        <v>-20.89658651494037</v>
       </c>
       <c r="F78">
-        <v>3.826686973457157</v>
+        <v>3.23956169590534</v>
       </c>
       <c r="G78">
-        <v>-8.280145641852149</v>
+        <v>-10.83793271531277</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.7005684545357953</v>
       </c>
       <c r="E79">
-        <v>-20.48055107938168</v>
+        <v>-22.25422755091395</v>
       </c>
       <c r="F79">
-        <v>3.76288942956315</v>
+        <v>3.880189567269171</v>
       </c>
       <c r="G79">
-        <v>-8.513873467470233</v>
+        <v>-9.610577751537836</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.5932651937771959</v>
       </c>
       <c r="E80">
-        <v>-22.75940599731362</v>
+        <v>-22.61285099300339</v>
       </c>
       <c r="F80">
-        <v>3.54422694298097</v>
+        <v>3.812558339035009</v>
       </c>
       <c r="G80">
-        <v>-8.488468341001868</v>
+        <v>-9.907576723502473</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.4394308163146605</v>
       </c>
       <c r="E81">
-        <v>-23.43221496605523</v>
+        <v>-22.53511973666172</v>
       </c>
       <c r="F81">
-        <v>3.745425787977331</v>
+        <v>3.470205688601612</v>
       </c>
       <c r="G81">
-        <v>-8.744194741728409</v>
+        <v>-10.33428949078683</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.2438856717891774</v>
       </c>
       <c r="E82">
-        <v>-24.04542015990788</v>
+        <v>-23.35806573265364</v>
       </c>
       <c r="F82">
-        <v>3.920065517305134</v>
+        <v>3.395412395802845</v>
       </c>
       <c r="G82">
-        <v>-7.066661863886757</v>
+        <v>-9.029610114851135</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.01066090579497206</v>
       </c>
       <c r="E83">
-        <v>-24.54176355351859</v>
+        <v>-24.07771270805658</v>
       </c>
       <c r="F83">
-        <v>3.577479267264148</v>
+        <v>3.802540063665551</v>
       </c>
       <c r="G83">
-        <v>-7.27041601019228</v>
+        <v>-9.101733659969698</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.2554282565949054</v>
       </c>
       <c r="E84">
-        <v>-25.39355140046536</v>
+        <v>-25.99644525900254</v>
       </c>
       <c r="F84">
-        <v>3.519609520504575</v>
+        <v>3.022625526990594</v>
       </c>
       <c r="G84">
-        <v>-7.896887095316263</v>
+        <v>-8.49036197305033</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.5488750449774628</v>
       </c>
       <c r="E85">
-        <v>-26.6475583087734</v>
+        <v>-26.43607404414119</v>
       </c>
       <c r="F85">
-        <v>3.954278747775559</v>
+        <v>3.364095137772606</v>
       </c>
       <c r="G85">
-        <v>-7.390522602357039</v>
+        <v>-9.760492495738193</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.8642457506550183</v>
       </c>
       <c r="E86">
-        <v>-26.96679761241813</v>
+        <v>-27.9843094941496</v>
       </c>
       <c r="F86">
-        <v>3.776115143516247</v>
+        <v>3.483603702974491</v>
       </c>
       <c r="G86">
-        <v>-6.770235616300414</v>
+        <v>-7.696824207287027</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.19656653405251</v>
       </c>
       <c r="E87">
-        <v>-27.29725394617986</v>
+        <v>-27.78501135307202</v>
       </c>
       <c r="F87">
-        <v>3.666987678606246</v>
+        <v>2.991811916341258</v>
       </c>
       <c r="G87">
-        <v>-7.29785050107622</v>
+        <v>-8.776823478563466</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.538951052923756</v>
       </c>
       <c r="E88">
-        <v>-28.10694057027731</v>
+        <v>-29.21109121672353</v>
       </c>
       <c r="F88">
-        <v>3.514183714016238</v>
+        <v>3.016959493955446</v>
       </c>
       <c r="G88">
-        <v>-6.823767137670429</v>
+        <v>-8.214043979069521</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.888829714652652</v>
       </c>
       <c r="E89">
-        <v>-29.73129513988065</v>
+        <v>-29.50416046907793</v>
       </c>
       <c r="F89">
-        <v>3.236889382663909</v>
+        <v>2.852821806560335</v>
       </c>
       <c r="G89">
-        <v>-7.597481356744577</v>
+        <v>-8.522043893861156</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.243234427537003</v>
       </c>
       <c r="E90">
-        <v>-31.76233611045384</v>
+        <v>-31.11100116545661</v>
       </c>
       <c r="F90">
-        <v>3.776963391736714</v>
+        <v>3.16848114580592</v>
       </c>
       <c r="G90">
-        <v>-6.481807646736951</v>
+        <v>-8.111734879723885</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.599059471501368</v>
       </c>
       <c r="E91">
-        <v>-32.90926272237651</v>
+        <v>-31.08094115499369</v>
       </c>
       <c r="F91">
-        <v>3.934132852539475</v>
+        <v>2.85712269011567</v>
       </c>
       <c r="G91">
-        <v>-7.10802381985441</v>
+        <v>-7.857249933574569</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.953052203183563</v>
       </c>
       <c r="E92">
-        <v>-35.25428543827152</v>
+        <v>-34.68098968584847</v>
       </c>
       <c r="F92">
-        <v>3.621533502479831</v>
+        <v>3.439980218808264</v>
       </c>
       <c r="G92">
-        <v>-6.68894517058361</v>
+        <v>-7.963511824294096</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.301502934627164</v>
       </c>
       <c r="E93">
-        <v>-36.73996228410098</v>
+        <v>-35.00590090318781</v>
       </c>
       <c r="F93">
-        <v>3.481049017904258</v>
+        <v>2.361311664844054</v>
       </c>
       <c r="G93">
-        <v>-7.047318346300795</v>
+        <v>-7.752640005079139</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.637033273888786</v>
       </c>
       <c r="E94">
-        <v>-37.28108096446253</v>
+        <v>-35.77090733848858</v>
       </c>
       <c r="F94">
-        <v>2.899319725614277</v>
+        <v>2.900500977530669</v>
       </c>
       <c r="G94">
-        <v>-6.26763852416488</v>
+        <v>-8.594495182988105</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.956702618741407</v>
       </c>
       <c r="E95">
-        <v>-39.47764671696408</v>
+        <v>-39.03391060590048</v>
       </c>
       <c r="F95">
-        <v>3.156360473968158</v>
+        <v>2.487677455406313</v>
       </c>
       <c r="G95">
-        <v>-7.687846007784524</v>
+        <v>-7.380673729377707</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.254485188018989</v>
       </c>
       <c r="E96">
-        <v>-41.48887561375371</v>
+        <v>-41.20183828877753</v>
       </c>
       <c r="F96">
-        <v>3.06358829505903</v>
+        <v>2.10729114404078</v>
       </c>
       <c r="G96">
-        <v>-6.321004518257932</v>
+        <v>-9.077066785156587</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.52538289506903</v>
       </c>
       <c r="E97">
-        <v>-42.92885562837176</v>
+        <v>-42.80027187316097</v>
       </c>
       <c r="F97">
-        <v>2.309522134821029</v>
+        <v>2.073067973161521</v>
       </c>
       <c r="G97">
-        <v>-7.825978520410613</v>
+        <v>-9.060454467640525</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.762775413378934</v>
       </c>
       <c r="E98">
-        <v>-45.27906571124256</v>
+        <v>-44.52839416041307</v>
       </c>
       <c r="F98">
-        <v>2.91932645512669</v>
+        <v>1.598695096274356</v>
       </c>
       <c r="G98">
-        <v>-6.631427752384313</v>
+        <v>-8.637499169543238</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.962271110605985</v>
       </c>
       <c r="E99">
-        <v>-46.99326973363209</v>
+        <v>-46.29516018060963</v>
       </c>
       <c r="F99">
-        <v>2.489473355935582</v>
+        <v>1.58027054850129</v>
       </c>
       <c r="G99">
-        <v>-8.139271997519542</v>
+        <v>-9.085293490821677</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>5.113152452756474</v>
       </c>
       <c r="E100">
-        <v>-49.94249277281551</v>
+        <v>-48.27773289387872</v>
       </c>
       <c r="F100">
-        <v>2.809695342835787</v>
+        <v>1.689026904814837</v>
       </c>
       <c r="G100">
-        <v>-7.184596738177753</v>
+        <v>-9.544982602222717</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>5.216612857416018</v>
       </c>
       <c r="E101">
-        <v>-50.94409272900252</v>
+        <v>-49.97463814555895</v>
       </c>
       <c r="F101">
-        <v>2.28034703489443</v>
+        <v>0.9005453924601272</v>
       </c>
       <c r="G101">
-        <v>-8.338414553888862</v>
+        <v>-9.254730522067115</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>5.261754985469851</v>
       </c>
       <c r="E102">
-        <v>-54.03835033734809</v>
+        <v>-51.59607864213836</v>
       </c>
       <c r="F102">
-        <v>1.78376562793821</v>
+        <v>0.5806050504768742</v>
       </c>
       <c r="G102">
-        <v>-8.50830844041872</v>
+        <v>-9.422346753265955</v>
       </c>
     </row>
   </sheetData>
